--- a/scripts/fct_test/FCT必须测试项 260821修改.xlsx
+++ b/scripts/fct_test/FCT必须测试项 260821修改.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JampMar\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14A97AD5-C829-4A26-9B9C-E5A0DA518100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3365F71D-1649-4DD6-AF85-538368CB4ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="744" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
     <t>烧录能成功 → 电源正常 → BLE能广播 → 5个接口信号通路完好 = PCBA合格，剩下的留给整机测试验证。</t>
   </si>
@@ -582,6 +582,10 @@
   </si>
   <si>
     <t>电池电压ADC  +-100mv即可  目前我测得4000mv 读出来4033mv</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Laser FCT治具外接上拉3V3 作为普通IO测试</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -848,16 +852,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>28212</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1040584</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>48986</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>747608</xdr:colOff>
+      <xdr:colOff>638751</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>101781</xdr:rowOff>
+      <xdr:rowOff>74568</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -880,7 +884,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1149441" y="4669971"/>
+          <a:off x="1040584" y="4849586"/>
           <a:ext cx="6608567" cy="4205696"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -905,7 +909,7 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>157395</xdr:rowOff>
+      <xdr:rowOff>157396</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1338,7 +1342,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>30</v>
       </c>
@@ -1432,6 +1436,11 @@
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C18" s="14" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
